--- a/documents/01_設計書/02_機能一覧_Always First.xlsx
+++ b/documents/01_設計書/02_機能一覧_Always First.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seplus2016-my.sharepoint.com/personal/furuhashi-nami-plusdojo2025_seplus2016_onmicrosoft_com/Documents/SEplus/研修/6月チーム開発/提出用/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="417" documentId="13_ncr:1_{D95A49AD-B3C8-44CA-A7AC-0C55C28AC17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBDEB8B2-C92F-4884-B74A-2B34AEA3BCBE}"/>
+  <xr:revisionPtr revIDLastSave="418" documentId="13_ncr:1_{D95A49AD-B3C8-44CA-A7AC-0C55C28AC17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC63C26-D06B-4D37-8375-A0C78D7D20BD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,13 +69,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>peace（仮）</t>
-    <rPh sb="6" eb="7">
-      <t>カリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>作成日</t>
     <rPh sb="0" eb="3">
       <t>サクセイビ</t>
@@ -782,6 +775,10 @@
     <rPh sb="0" eb="2">
       <t>カワカミ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TABI×TILE</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -941,7 +938,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1002,12 +999,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1023,10 +1014,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1350,10 +1337,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="H3" s="19">
         <v>45820</v>
@@ -1362,55 +1349,53 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G4" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G5" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G6" s="21"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
+      <c r="H6"/>
     </row>
     <row r="7" spans="2:9" ht="21" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>9</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1418,25 +1403,25 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1444,25 +1429,25 @@
         <v>2</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>26</v>
-      </c>
       <c r="I10" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -1480,25 +1465,25 @@
         <v>3</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="H12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>30</v>
-      </c>
       <c r="I12" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1506,25 +1491,25 @@
         <v>4</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="I13" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -1542,23 +1527,23 @@
         <v>5</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="G15" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>36</v>
-      </c>
       <c r="I15" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1566,23 +1551,23 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1590,23 +1575,23 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1614,23 +1599,23 @@
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1638,23 +1623,23 @@
         <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1662,23 +1647,23 @@
         <v>10</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" s="9" t="s">
+      <c r="H20" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="I20" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -1696,25 +1681,25 @@
         <v>11</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="G22" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>55</v>
-      </c>
       <c r="I22" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1722,25 +1707,25 @@
         <v>12</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="I23" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -1758,25 +1743,25 @@
         <v>13</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="I25" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -1794,25 +1779,25 @@
         <v>14</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="11" t="s">
+      <c r="F27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="G27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>65</v>
-      </c>
       <c r="I27" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1820,25 +1805,25 @@
         <v>15</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E28" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="G28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="I28" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -1856,25 +1841,25 @@
         <v>16</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="I30" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -1892,25 +1877,25 @@
         <v>17</v>
       </c>
       <c r="C32" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F32" s="11" t="s">
+      <c r="G32" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>74</v>
-      </c>
       <c r="I32" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1918,25 +1903,25 @@
         <v>18</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="G33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="I33" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1944,25 +1929,25 @@
         <v>19</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="I34" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -1970,25 +1955,25 @@
         <v>20</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" s="9" t="s">
+      <c r="G35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="I35" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -2006,25 +1991,25 @@
         <v>21</v>
       </c>
       <c r="C37" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="11" t="s">
+      <c r="G37" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="G37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>82</v>
-      </c>
       <c r="I37" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2032,25 +2017,25 @@
         <v>22</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="G38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="I38" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2058,25 +2043,25 @@
         <v>23</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="G39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I39" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2084,25 +2069,25 @@
         <v>24</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>86</v>
-      </c>
       <c r="G40" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -2120,25 +2105,25 @@
         <v>25</v>
       </c>
       <c r="C42" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>90</v>
-      </c>
       <c r="I42" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2146,25 +2131,25 @@
         <v>26</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="I43" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2172,25 +2157,25 @@
         <v>27</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D44" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="I44" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2198,25 +2183,25 @@
         <v>28</v>
       </c>
       <c r="C45" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>94</v>
-      </c>
       <c r="G45" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="2:9" ht="7.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -2234,25 +2219,25 @@
         <v>29</v>
       </c>
       <c r="C47" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="11" t="s">
+      <c r="G47" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H47" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="G47" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H47" s="12" t="s">
-        <v>99</v>
-      </c>
       <c r="I47" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2260,25 +2245,25 @@
         <v>30</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D48" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="G48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="I48" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2286,25 +2271,25 @@
         <v>31</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="G49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I49" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2312,25 +2297,25 @@
         <v>32</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="I50" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2338,25 +2323,25 @@
         <v>33</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="G51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2364,25 +2349,25 @@
         <v>34</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D52" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="G52" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
@@ -2390,25 +2375,25 @@
         <v>35</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D53" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="G53" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="I53" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
